--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -913,11 +913,11 @@
         <v>116227207</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1023,11 +1023,11 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56481</v>
+        <v>56566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>116227207</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>116227207</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>56570</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>116227207</v>
       </c>
       <c r="B4" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56570</v>
+        <v>56571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56572</v>
+        <v>56592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -1038,11 +1038,6 @@
       <c r="E5" t="n">
         <v>102613</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lyrurus tetrix</t>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56592</v>
+        <v>56596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,6 +1037,11 @@
       </c>
       <c r="E5" t="n">
         <v>102613</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1254,6 +1254,120 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122923737</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 12131-2024, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>360304</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6392505</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>122923737</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>122923737</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -675,65 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116227223</v>
+        <v>116223798</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 12131-2024, Vg</t>
+          <t>Hulatjärnen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>360185</v>
+        <v>360258</v>
       </c>
       <c r="R2" t="n">
-        <v>6392430</v>
+        <v>6392464</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,55 +757,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Tobias Federsel</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Tobias Federsel, Christer Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116223798</v>
+        <v>116219694</v>
       </c>
       <c r="B3" t="n">
-        <v>90382</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>360258</v>
+        <v>360303</v>
       </c>
       <c r="R3" t="n">
-        <v>6392464</v>
+        <v>6392479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +900,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Federsel, Christer Johansson</t>
+          <t>Tobias Federsel</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -913,12 +910,7 @@
         <v>116227207</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,12 +1015,7 @@
         <v>116227233</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,56 +1122,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116219694</v>
+        <v>116227223</v>
       </c>
       <c r="B6" t="n">
-        <v>74595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hulatjärnen, Vg</t>
+          <t>A 12131-2024, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360303</v>
+        <v>360185</v>
       </c>
       <c r="R6" t="n">
-        <v>6392479</v>
+        <v>6392430</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,34 +1213,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1259,12 +1234,7 @@
         <v>122923737</v>
       </c>
       <c r="B7" t="n">
-        <v>57640</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12131-2024 artfynd.xlsx
+++ b/artfynd/A 12131-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116223798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116219694</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116227207</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116227233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116227223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,8 +1367,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122923737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>